--- a/scripts/python/sf-doc-mcp/プログラム設計書（画面）テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/プログラム設計書（画面）テンプレート.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改版履歴" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面概要" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面項目定義" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理詳細" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パラメーター定義" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="改版履歴" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="画面概要" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="画面項目定義" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="処理詳細" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="パラメーター定義" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -301,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -336,6 +336,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1493,9 +1494,9 @@
   </sheetData>
   <mergeCells count="173">
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="AD17:AE17"/>
     <mergeCell ref="R24:W24"/>
     <mergeCell ref="AA5:AC5"/>
+    <mergeCell ref="AD17:AE17"/>
     <mergeCell ref="L15:Q15"/>
     <mergeCell ref="X18:Z18"/>
     <mergeCell ref="L18:Q18"/>
@@ -2640,69 +2641,71 @@
       <c r="AD39" s="18" t="n"/>
       <c r="AE39" s="18" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="14" t="n"/>
-      <c r="D40" s="14" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="14" t="n"/>
-      <c r="G40" s="14" t="n"/>
-      <c r="H40" s="14" t="n"/>
-      <c r="I40" s="14" t="n"/>
-      <c r="J40" s="14" t="n"/>
-      <c r="K40" s="14" t="n"/>
-      <c r="L40" s="14" t="n"/>
-      <c r="M40" s="14" t="n"/>
-      <c r="N40" s="14" t="n"/>
-      <c r="O40" s="14" t="n"/>
-      <c r="P40" s="14" t="n"/>
-      <c r="Q40" s="14" t="n"/>
-      <c r="R40" s="14" t="n"/>
-      <c r="S40" s="14" t="n"/>
-      <c r="T40" s="14" t="n"/>
-      <c r="U40" s="14" t="n"/>
-      <c r="V40" s="14" t="n"/>
-      <c r="W40" s="14" t="n"/>
-      <c r="X40" s="14" t="n"/>
-      <c r="Y40" s="14" t="n"/>
-      <c r="Z40" s="14" t="n"/>
-      <c r="AA40" s="14" t="n"/>
-      <c r="AB40" s="14" t="n"/>
-      <c r="AC40" s="14" t="n"/>
-      <c r="AD40" s="14" t="n"/>
-      <c r="AE40" s="14" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="15" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="16" t="n"/>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
-      <c r="M41" s="16" t="n"/>
-      <c r="N41" s="16" t="n"/>
-      <c r="O41" s="16" t="n"/>
-      <c r="P41" s="16" t="n"/>
-      <c r="Q41" s="16" t="n"/>
-      <c r="R41" s="16" t="n"/>
-      <c r="S41" s="16" t="n"/>
-      <c r="T41" s="16" t="n"/>
-      <c r="U41" s="16" t="n"/>
-      <c r="V41" s="16" t="n"/>
-      <c r="W41" s="16" t="n"/>
-      <c r="X41" s="16" t="n"/>
-      <c r="Y41" s="16" t="n"/>
-      <c r="Z41" s="16" t="n"/>
-      <c r="AA41" s="16" t="n"/>
-      <c r="AB41" s="16" t="n"/>
-      <c r="AC41" s="16" t="n"/>
-      <c r="AD41" s="16" t="n"/>
-      <c r="AE41" s="17" t="n"/>
+    <row r="40">
+      <c r="A40" s="20" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
+      <c r="L40" s="20" t="n"/>
+      <c r="M40" s="20" t="n"/>
+      <c r="N40" s="20" t="n"/>
+      <c r="O40" s="20" t="n"/>
+      <c r="P40" s="20" t="n"/>
+      <c r="Q40" s="20" t="n"/>
+      <c r="R40" s="20" t="n"/>
+      <c r="S40" s="20" t="n"/>
+      <c r="T40" s="20" t="n"/>
+      <c r="U40" s="20" t="n"/>
+      <c r="V40" s="20" t="n"/>
+      <c r="W40" s="20" t="n"/>
+      <c r="X40" s="20" t="n"/>
+      <c r="Y40" s="20" t="n"/>
+      <c r="Z40" s="20" t="n"/>
+      <c r="AA40" s="20" t="n"/>
+      <c r="AB40" s="20" t="n"/>
+      <c r="AC40" s="20" t="n"/>
+      <c r="AD40" s="20" t="n"/>
+      <c r="AE40" s="20" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="20" t="n"/>
+      <c r="K41" s="20" t="n"/>
+      <c r="L41" s="20" t="n"/>
+      <c r="M41" s="20" t="n"/>
+      <c r="N41" s="20" t="n"/>
+      <c r="O41" s="20" t="n"/>
+      <c r="P41" s="20" t="n"/>
+      <c r="Q41" s="20" t="n"/>
+      <c r="R41" s="20" t="n"/>
+      <c r="S41" s="20" t="n"/>
+      <c r="T41" s="20" t="n"/>
+      <c r="U41" s="20" t="n"/>
+      <c r="V41" s="20" t="n"/>
+      <c r="W41" s="20" t="n"/>
+      <c r="X41" s="20" t="n"/>
+      <c r="Y41" s="20" t="n"/>
+      <c r="Z41" s="20" t="n"/>
+      <c r="AA41" s="20" t="n"/>
+      <c r="AB41" s="20" t="n"/>
+      <c r="AC41" s="20" t="n"/>
+      <c r="AD41" s="20" t="n"/>
+      <c r="AE41" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="25">
